--- a/paf_geneva_odds.xlsx
+++ b/paf_geneva_odds.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="D2" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="3">
